--- a/Automated_Pipeline/INPUT_EXCEL/DIS/DIS Theme 6 - Climate Change and Environmental Risk.xlsx
+++ b/Automated_Pipeline/INPUT_EXCEL/DIS/DIS Theme 6 - Climate Change and Environmental Risk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin\Desktop\June_12_Update_ADM1_2_3_New_SHP\Automated_Pipeline\INPUT_EXCEL\DIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin\Documents\GitHub\LB_DEV\Automated_Pipeline\INPUT_EXCEL\DIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2620AA0-32F4-4A31-A1E8-908BC86E9CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A6313D-B9AE-4A42-9629-DF47E3E23233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Beirut</t>
   </si>
@@ -111,10 +111,25 @@
     <t>Annual Dry Spell Length</t>
   </si>
   <si>
-    <t>Mean annual hot days</t>
-  </si>
-  <si>
     <t>Forest fire risk</t>
+  </si>
+  <si>
+    <t>Hot days (Tmax &gt; 30°C)</t>
+  </si>
+  <si>
+    <t>Very Hot Days (Tmax &gt; 35°C)</t>
+  </si>
+  <si>
+    <t>Days withh at least 20 mm rainfall</t>
+  </si>
+  <si>
+    <t>Days withh at least 10 mm rainfall</t>
+  </si>
+  <si>
+    <t>Consecutive Wet Days</t>
+  </si>
+  <si>
+    <t>Consecutive Dry Days</t>
   </si>
 </sst>
 </file>
@@ -432,16 +447,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -449,378 +468,783 @@
         <v>28</v>
       </c>
       <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2">
-        <v>5.12505882856287</v>
+        <v>142</v>
       </c>
       <c r="C2">
-        <v>142</v>
+        <v>25.770204937320699</v>
       </c>
       <c r="D2">
-        <v>25.770204937320699</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>123.115246</v>
+      </c>
+      <c r="E2">
+        <v>8.0917630000000003</v>
+      </c>
+      <c r="F2">
+        <v>27.687256000000001</v>
+      </c>
+      <c r="G2">
+        <v>10.776996</v>
+      </c>
+      <c r="H2">
+        <v>3.9817279999999999</v>
+      </c>
+      <c r="I2">
+        <v>24.958344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.86304710563470699</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>73</v>
+        <v>27.034912078038701</v>
       </c>
       <c r="D3">
-        <v>27.034912078038701</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>145.652298</v>
+      </c>
+      <c r="E3">
+        <v>7.6167999999999996</v>
+      </c>
+      <c r="F3">
+        <v>29.011655999999999</v>
+      </c>
+      <c r="G3">
+        <v>14.120979999999999</v>
+      </c>
+      <c r="H3">
+        <v>1.5881670000000001</v>
+      </c>
+      <c r="I3">
+        <v>27.277121000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.77580813347236799</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>51</v>
+        <v>27.3524504692388</v>
       </c>
       <c r="D4">
-        <v>27.3524504692388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>144.49559500000001</v>
+      </c>
+      <c r="E4">
+        <v>7.7997199999999998</v>
+      </c>
+      <c r="F4">
+        <v>28.740888999999999</v>
+      </c>
+      <c r="G4">
+        <v>13.716993</v>
+      </c>
+      <c r="H4">
+        <v>1.4140790000000001</v>
+      </c>
+      <c r="I4">
+        <v>27.256836</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>3.0444706808343298</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>28.938213301849601</v>
       </c>
       <c r="D5">
-        <v>28.938213301849601</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>134.20904100000001</v>
+      </c>
+      <c r="E5">
+        <v>8.0566980000000008</v>
+      </c>
+      <c r="F5">
+        <v>22.073775000000001</v>
+      </c>
+      <c r="G5">
+        <v>7.6980190000000004</v>
+      </c>
+      <c r="H5">
+        <v>0.72944100000000001</v>
+      </c>
+      <c r="I5">
+        <v>27.798217000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6">
-        <v>4.7826991058432097E-3</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>25.476190476190499</v>
       </c>
       <c r="D6">
-        <v>25.476190476190499</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>126.77536600000001</v>
+      </c>
+      <c r="E6">
+        <v>8.7614850000000004</v>
+      </c>
+      <c r="F6">
+        <v>30.289421999999998</v>
+      </c>
+      <c r="G6">
+        <v>12.703735</v>
+      </c>
+      <c r="H6">
+        <v>3.2550000000000003E-2</v>
+      </c>
+      <c r="I6">
+        <v>25.784295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7">
-        <v>1.5499231950844901</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>24.399385560675899</v>
       </c>
       <c r="D7">
-        <v>24.399385560675899</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>144.11999499999999</v>
+      </c>
+      <c r="E7">
+        <v>7.62</v>
+      </c>
+      <c r="F7">
+        <v>29.309999000000001</v>
+      </c>
+      <c r="G7">
+        <v>14.63</v>
+      </c>
+      <c r="H7">
+        <v>2.1150000000000002</v>
+      </c>
+      <c r="I7">
+        <v>24.548683</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.476190476190476</v>
+        <v>35</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>15.788969743393301</v>
       </c>
       <c r="D8">
-        <v>15.788969743393301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>158.36603199999999</v>
+      </c>
+      <c r="E8">
+        <v>7.5406089999999999</v>
+      </c>
+      <c r="F8">
+        <v>25.251898000000001</v>
+      </c>
+      <c r="G8">
+        <v>12.344519</v>
+      </c>
+      <c r="H8">
+        <v>1.479385</v>
+      </c>
+      <c r="I8">
+        <v>15.769302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.60859985785358905</v>
+        <v>93</v>
       </c>
       <c r="C9">
-        <v>93</v>
+        <v>24.208315565031999</v>
       </c>
       <c r="D9">
-        <v>24.208315565031999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147.99665100000001</v>
+      </c>
+      <c r="E9">
+        <v>7.6653510000000002</v>
+      </c>
+      <c r="F9">
+        <v>29.190259000000001</v>
+      </c>
+      <c r="G9">
+        <v>14.531141999999999</v>
+      </c>
+      <c r="H9">
+        <v>1.2596290000000001</v>
+      </c>
+      <c r="I9">
+        <v>24.489405000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10">
-        <v>2.07570207570208E-3</v>
+        <v>72</v>
       </c>
       <c r="C10">
-        <v>72</v>
+        <v>25.8115995115995</v>
       </c>
       <c r="D10">
-        <v>25.8115995115995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>127.904984</v>
+      </c>
+      <c r="E10">
+        <v>8.5793560000000006</v>
+      </c>
+      <c r="F10">
+        <v>30.320616000000001</v>
+      </c>
+      <c r="G10">
+        <v>14.047859000000001</v>
+      </c>
+      <c r="H10">
+        <v>8.3363000000000007E-2</v>
+      </c>
+      <c r="I10">
+        <v>25.937669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>2.56222651222651</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>28.398198198198202</v>
       </c>
       <c r="D11">
-        <v>28.398198198198202</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>126.471559</v>
+      </c>
+      <c r="E11">
+        <v>8.0930470000000003</v>
+      </c>
+      <c r="F11">
+        <v>24.358885999999998</v>
+      </c>
+      <c r="G11">
+        <v>8.3449570000000008</v>
+      </c>
+      <c r="H11">
+        <v>0.94709200000000004</v>
+      </c>
+      <c r="I11">
+        <v>27.488837</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12">
-        <v>0.104571428571428</v>
+        <v>41</v>
       </c>
       <c r="C12">
-        <v>41</v>
+        <v>28.3247619047619</v>
       </c>
       <c r="D12">
-        <v>28.3247619047619</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>126.573729</v>
+      </c>
+      <c r="E12">
+        <v>8.3806860000000007</v>
+      </c>
+      <c r="F12">
+        <v>29.911930999999999</v>
+      </c>
+      <c r="G12">
+        <v>13.559407999999999</v>
+      </c>
+      <c r="H12">
+        <v>0.217811</v>
+      </c>
+      <c r="I12">
+        <v>27.881357000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0.47606142728093997</v>
+        <v>94</v>
       </c>
       <c r="C13">
-        <v>94</v>
+        <v>26.181055620079999</v>
       </c>
       <c r="D13">
-        <v>26.181055620079999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>140.776892</v>
+      </c>
+      <c r="E13">
+        <v>8.0080349999999996</v>
+      </c>
+      <c r="F13">
+        <v>29.054466999999999</v>
+      </c>
+      <c r="G13">
+        <v>13.937609999999999</v>
+      </c>
+      <c r="H13">
+        <v>0.98685999999999996</v>
+      </c>
+      <c r="I13">
+        <v>26.690407</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14">
-        <v>0.79803594589586702</v>
+        <v>53</v>
       </c>
       <c r="C14">
-        <v>53</v>
+        <v>25.7887715397443</v>
       </c>
       <c r="D14">
-        <v>25.7887715397443</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>125.441807</v>
+      </c>
+      <c r="E14">
+        <v>8.1899680000000004</v>
+      </c>
+      <c r="F14">
+        <v>30.167556000000001</v>
+      </c>
+      <c r="G14">
+        <v>12.428436</v>
+      </c>
+      <c r="H14">
+        <v>0.51418399999999997</v>
+      </c>
+      <c r="I14">
+        <v>25.855961000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.32285045165607201</v>
+        <v>42</v>
       </c>
       <c r="C15">
-        <v>42</v>
+        <v>17.049626407940199</v>
       </c>
       <c r="D15">
-        <v>17.049626407940199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>154.991151</v>
+      </c>
+      <c r="E15">
+        <v>7.5132919999999999</v>
+      </c>
+      <c r="F15">
+        <v>27.877129</v>
+      </c>
+      <c r="G15">
+        <v>14.141757999999999</v>
+      </c>
+      <c r="H15">
+        <v>1.4762500000000001</v>
+      </c>
+      <c r="I15">
+        <v>17.544267000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
       <c r="B16">
-        <v>1.78255258743064</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>23</v>
+        <v>26.376435669118599</v>
       </c>
       <c r="D16">
-        <v>26.376435669118599</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>153.64271500000001</v>
+      </c>
+      <c r="E16">
+        <v>7.6485580000000004</v>
+      </c>
+      <c r="F16">
+        <v>26.93141</v>
+      </c>
+      <c r="G16">
+        <v>12.987916999999999</v>
+      </c>
+      <c r="H16">
+        <v>1.7826390000000001</v>
+      </c>
+      <c r="I16">
+        <v>26.270299999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17">
-        <v>1.3400335008375199E-2</v>
+        <v>92</v>
       </c>
       <c r="C17">
-        <v>92</v>
+        <v>24.8884103054957</v>
       </c>
       <c r="D17">
-        <v>24.8884103054957</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>130.61393799999999</v>
+      </c>
+      <c r="E17">
+        <v>8.5941349999999996</v>
+      </c>
+      <c r="F17">
+        <v>30.470139</v>
+      </c>
+      <c r="G17">
+        <v>14.315855000000001</v>
+      </c>
+      <c r="H17">
+        <v>8.0157000000000006E-2</v>
+      </c>
+      <c r="I17">
+        <v>25.106204999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18">
-        <v>0.393557422969189</v>
+        <v>74</v>
       </c>
       <c r="C18">
-        <v>74</v>
+        <v>22.603361344537799</v>
       </c>
       <c r="D18">
-        <v>22.603361344537799</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>151.84224900000001</v>
+      </c>
+      <c r="E18">
+        <v>7.6622709999999996</v>
+      </c>
+      <c r="F18">
+        <v>28.964583000000001</v>
+      </c>
+      <c r="G18">
+        <v>14.724729999999999</v>
+      </c>
+      <c r="H18">
+        <v>1.206976</v>
+      </c>
+      <c r="I18">
+        <v>21.757724</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>10</v>
       </c>
       <c r="B19">
-        <v>0.106994665085951</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>74</v>
+        <v>25.1321873147599</v>
       </c>
       <c r="D19">
-        <v>25.1321873147599</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>135.04321300000001</v>
+      </c>
+      <c r="E19">
+        <v>8.3427910000000001</v>
+      </c>
+      <c r="F19">
+        <v>29.742176000000001</v>
+      </c>
+      <c r="G19">
+        <v>14.263973</v>
+      </c>
+      <c r="H19">
+        <v>0.41221999999999998</v>
+      </c>
+      <c r="I19">
+        <v>25.744067999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
       <c r="B20">
-        <v>1.1070455430128401</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>25</v>
+        <v>21.798884131309201</v>
       </c>
       <c r="D20">
-        <v>21.798884131309201</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>155.96913699999999</v>
+      </c>
+      <c r="E20">
+        <v>7.5315770000000004</v>
+      </c>
+      <c r="F20">
+        <v>26.571558</v>
+      </c>
+      <c r="G20">
+        <v>13.038557000000001</v>
+      </c>
+      <c r="H20">
+        <v>1.898949</v>
+      </c>
+      <c r="I20">
+        <v>21.346074999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
       <c r="B21">
-        <v>0.63042397115504001</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>33.431306726345902</v>
       </c>
       <c r="D21">
-        <v>33.431306726345902</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>150.92096599999999</v>
+      </c>
+      <c r="E21">
+        <v>7.7343500000000001</v>
+      </c>
+      <c r="F21">
+        <v>24.624103999999999</v>
+      </c>
+      <c r="G21">
+        <v>10.656765999999999</v>
+      </c>
+      <c r="H21">
+        <v>1.6257269999999999</v>
+      </c>
+      <c r="I21">
+        <v>31.754863</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22">
-        <v>0.139012896825397</v>
+        <v>50</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>14.455853174603201</v>
       </c>
       <c r="D22">
-        <v>14.455853174603201</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>153.88314199999999</v>
+      </c>
+      <c r="E22">
+        <v>7.5285279999999997</v>
+      </c>
+      <c r="F22">
+        <v>28.102499999999999</v>
+      </c>
+      <c r="G22">
+        <v>14.375214</v>
+      </c>
+      <c r="H22">
+        <v>1.450013</v>
+      </c>
+      <c r="I22">
+        <v>15.337723</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23">
-        <v>1.21333000914153E-2</v>
+        <v>55</v>
       </c>
       <c r="C23">
-        <v>55</v>
+        <v>13.7679714119505</v>
       </c>
       <c r="D23">
-        <v>13.7679714119505</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>158.965025</v>
+      </c>
+      <c r="E23">
+        <v>7.521935</v>
+      </c>
+      <c r="F23">
+        <v>25.589480999999999</v>
+      </c>
+      <c r="G23">
+        <v>12.584747</v>
+      </c>
+      <c r="H23">
+        <v>1.4049259999999999</v>
+      </c>
+      <c r="I23">
+        <v>13.851043000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
       <c r="B24">
-        <v>0.69719169719169705</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>32.500610500610499</v>
       </c>
       <c r="D24">
-        <v>32.500610500610499</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>125.043571</v>
+      </c>
+      <c r="E24">
+        <v>8.1940770000000001</v>
+      </c>
+      <c r="F24">
+        <v>29.440154</v>
+      </c>
+      <c r="G24">
+        <v>13.046654</v>
+      </c>
+      <c r="H24">
+        <v>0.37826900000000002</v>
+      </c>
+      <c r="I24">
+        <v>32.104416000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
       <c r="B25">
-        <v>1.20826353992183</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>31.8028236420196</v>
       </c>
       <c r="D25">
-        <v>31.8028236420196</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>148.19439600000001</v>
+      </c>
+      <c r="E25">
+        <v>7.8205669999999996</v>
+      </c>
+      <c r="F25">
+        <v>26.576898</v>
+      </c>
+      <c r="G25">
+        <v>11.905321000000001</v>
+      </c>
+      <c r="H25">
+        <v>1.581175</v>
+      </c>
+      <c r="I25">
+        <v>31.055875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
       <c r="B26">
-        <v>2.7732463295269101</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>30.043035811388201</v>
       </c>
       <c r="D26">
-        <v>30.043035811388201</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>144.168319</v>
+      </c>
+      <c r="E26">
+        <v>7.9857800000000001</v>
+      </c>
+      <c r="F26">
+        <v>24.302524999999999</v>
+      </c>
+      <c r="G26">
+        <v>9.5730780000000006</v>
+      </c>
+      <c r="H26">
+        <v>1.5261199999999999</v>
+      </c>
+      <c r="I26">
+        <v>30.444572999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
       <c r="B27">
-        <v>0.77442610510339605</v>
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>31</v>
+        <v>26.6884841586037</v>
       </c>
       <c r="D27">
-        <v>26.6884841586037</v>
+        <v>126.317055</v>
+      </c>
+      <c r="E27">
+        <v>8.2696649999999998</v>
+      </c>
+      <c r="F27">
+        <v>30.053089</v>
+      </c>
+      <c r="G27">
+        <v>12.817174</v>
+      </c>
+      <c r="H27">
+        <v>0.308585</v>
+      </c>
+      <c r="I27">
+        <v>26.849416000000002</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B27">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A27">
     <sortCondition ref="A1:A27"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
